--- a/intern_schedule_2026-2027/schedules/TYP_September_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_September_2026.xlsx
@@ -1169,12 +1169,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr, LI</t>
+          <t>WISE, LI</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
+          <t>WISE</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>BUTT, LI</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
           <t>AHLUWALIA Sr</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>BUTT, LI</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>BUTT, AHLUWALIA Sr</t>
+          <t>BUTT, WISE</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_September_2026.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_September_2026.xlsx
@@ -1169,12 +1169,12 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>WISE, LI</t>
+          <t>AHLUWALIA Sr, LI</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>WISE</t>
+          <t>AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>WISE</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>BUTT, WISE</t>
+          <t>BUTT, AHLUWALIA Sr</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sr</t>
+          <t>WISE</t>
         </is>
       </c>
     </row>
